--- a/artfynd/A 40999-2021 artfynd.xlsx
+++ b/artfynd/A 40999-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40999-2021 artfynd.xlsx
+++ b/artfynd/A 40999-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>77093229</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397053.0607906376</v>
+        <v>397053</v>
       </c>
       <c r="R2" t="n">
-        <v>6171361.308358897</v>
+        <v>6171361</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -799,62 +794,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86226420</v>
+        <v>102400100</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrylleskogen, Sk</t>
+          <t>Brända tomten, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397163.4438214865</v>
+        <v>396995</v>
       </c>
       <c r="R3" t="n">
-        <v>6171129.173349777</v>
+        <v>6171191</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,27 +866,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Satt nertill i en stor gran strax intill promenadspåret (Skrylle). Såg den på ca 15 meters avstånd och kunde särskilja från entita med hjälp av lätet</t>
+          <t>Slukar en liten vanlig groda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +891,596 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Håkan Sandsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Sandsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>80653710</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brända tomten, Dalby, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>397053</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6171361</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-10-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-10-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99636152</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granskogen V Stora hygget, Skryllegården, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>397089</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6171417</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>O om längs spåret vid unggranar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116720151</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brända tomten, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>397017</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6171298</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Viktor Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Viktor Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86226420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skrylleskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>397163</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6171129</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt nertill i en stor gran strax intill promenadspåret (Skrylle). Såg den på ca 15 meters avstånd och kunde särskilja från entita med hjälp av lätet</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Oscar Stahle</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Oscar Stahle</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102400108</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brända tomten, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>396995</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6171191</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Slukas av en snok</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Sandsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Sandsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
